--- a/examples/EXCEL/MonsterTable.xlsx
+++ b/examples/EXCEL/MonsterTable.xlsx
@@ -7,16 +7,24 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="38370" windowHeight="6405" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MonsterTable" sheetId="1" r:id="rId1"/>
-    <sheet name="MonsterDrop" sheetId="2" r:id="rId2"/>
-    <sheet name="MonsterTest" sheetId="3" r:id="rId3"/>
+    <sheet name="MonsterRace" sheetId="1" r:id="rId1"/>
+    <sheet name="Monster" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>MonsterID</t>
+  </si>
+  <si>
+    <t>Memo</t>
+  </si>
   <si>
     <t>monsterId</t>
   </si>
@@ -36,25 +44,7 @@
     <t>moveSpeed</t>
   </si>
   <si>
-    <t>rewardItemId</t>
-  </si>
-  <si>
-    <t>itemId</t>
-  </si>
-  <si>
-    <t>dropRate</t>
-  </si>
-  <si>
-    <t>minCount</t>
-  </si>
-  <si>
-    <t>maxCount</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>MonsterDrop</t>
+    <t>RewardGroupId</t>
   </si>
   <si>
     <t>고블린</t>
@@ -407,126 +397,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>1555</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="5" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>35</v>
-      </c>
-      <c r="C2">
-        <v>0.1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>36</v>
-      </c>
-      <c r="C3">
-        <v>0.1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -536,11 +434,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 참조" error="MonsterTable 시트의 값을 선택하세요.">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 참조" error="Monster 시트의 값을 선택하세요.">
           <x14:formula1>
-            <xm:f>OFFSET(MonsterTable!$A$2,0,0,MAX(1,COUNTA(MonsterTable!$A$2:$A$21)),1)</xm:f>
+            <xm:f>OFFSET(Monster!$A$2,0,0,MAX(1,COUNTA(Monster!$A$2:$A$21)),1)</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A10000</xm:sqref>
+          <xm:sqref>B2:B10000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -548,46 +446,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10000</v>
+      </c>
+      <c r="C2">
         <v>100</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 참조" error="MonsterDrop 시트의 값을 선택하세요.">
-          <x14:formula1>
-            <xm:f>OFFSET(MonsterDrop!$A$2,0,0,MAX(1,COUNTA(MonsterDrop!$A$2:$A$21)),1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B10000</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>